--- a/bank_fintech_research/data/analysis/analysis_results.xlsx
+++ b/bank_fintech_research/data/analysis/analysis_results.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,26 @@
           <t>fai</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>fai_strategy</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>fai_algorithm</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>fai_risk_model</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fai_credit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -559,10 +579,22 @@
         <v>428265</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>4.5957</v>
+        <v>4.3171</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>3.9342</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.3133</v>
       </c>
     </row>
     <row r="3">
@@ -592,10 +624,22 @@
         <v>461286</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>5.0743</v>
+        <v>4.7012</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>3.8804</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0.597</v>
       </c>
     </row>
     <row r="4">
@@ -625,10 +669,22 @@
         <v>491000</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>5.4022</v>
+        <v>5.0978</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>4.4891</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.4946</v>
       </c>
     </row>
     <row r="5">
@@ -658,10 +714,22 @@
         <v>365261</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>4.8581</v>
+        <v>4.8277</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>4.2205</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.1215</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.2733</v>
       </c>
     </row>
     <row r="6">
@@ -691,10 +759,22 @@
         <v>396810</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>3.6649</v>
+        <v>3.4514</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>3.2023</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.0712</v>
       </c>
     </row>
     <row r="7">
@@ -724,10 +804,22 @@
         <v>421000</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>4.6321</v>
+        <v>4.5964</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>4.1689</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0.3563</v>
       </c>
     </row>
     <row r="8">
@@ -757,10 +849,22 @@
         <v>358059</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.7038</v>
+        <v>1.7763</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>1.3775</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.1813</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.145</v>
       </c>
     </row>
     <row r="9">
@@ -790,10 +894,22 @@
         <v>395640</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>2.457</v>
+        <v>2.2709</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2.0847</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0.0745</v>
       </c>
     </row>
     <row r="10">
@@ -823,10 +939,22 @@
         <v>422000</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.8709</v>
+        <v>2.7218</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>2.5354</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0.0746</v>
       </c>
     </row>
     <row r="11">
@@ -856,10 +984,22 @@
         <v>298124</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>3.5354</v>
+        <v>3.367</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>3.0977</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.101</v>
       </c>
     </row>
     <row r="12">
@@ -889,10 +1029,22 @@
         <v>328419</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>4.0193</v>
+        <v>3.8842</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>3.5127</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0.2027</v>
       </c>
     </row>
     <row r="13">
@@ -922,10 +1074,22 @@
         <v>350000</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>3.6729</v>
+        <v>3.6016</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>3.4233</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.1426</v>
       </c>
     </row>
     <row r="14">
@@ -955,10 +1119,22 @@
         <v>145360</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.7848</v>
+        <v>2.6637</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>2.4216</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0.1614</v>
       </c>
     </row>
     <row r="15">
@@ -988,10 +1164,22 @@
         <v>160272</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>4.0264</v>
+        <v>3.8604</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>3.4868</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0.083</v>
       </c>
     </row>
     <row r="16">
@@ -1021,10 +1209,22 @@
         <v>170000</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.4442</v>
+        <v>4.278</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>3.6966</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0.2907</v>
       </c>
     </row>
     <row r="17">
@@ -1054,10 +1254,22 @@
         <v>156508</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>7.3159</v>
+        <v>7.0697</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>5.2407</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1.1959</v>
       </c>
     </row>
     <row r="18">
@@ -1087,10 +1299,22 @@
         <v>172010</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7.4389</v>
+        <v>7.4019</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>5.5885</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0.6662</v>
       </c>
     </row>
     <row r="19">
@@ -1120,10 +1344,22 @@
         <v>183000</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>8.2918</v>
+        <v>7.7124</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>6.3727</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.5069</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0.6518</v>
       </c>
     </row>
     <row r="20">
@@ -1153,10 +1389,22 @@
         <v>57254</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.3899</v>
+        <v>4.6481</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>4.4009</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0.0989</v>
       </c>
     </row>
     <row r="21">
@@ -1186,10 +1434,22 @@
         <v>61016</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>5.6512</v>
+        <v>5.0233</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>4.7335</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1219,10 +1479,22 @@
         <v>63000</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>5.4956</v>
+        <v>5.1491</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>4.9015</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0.099</v>
       </c>
     </row>
     <row r="23">
@@ -1252,10 +1524,22 @@
         <v>68815</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>4.1288</v>
+        <v>3.6297</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>3.2213</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.1815</v>
       </c>
     </row>
     <row r="24">
@@ -1285,10 +1569,22 @@
         <v>72680</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4.2322</v>
+        <v>3.231</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2.9125</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0.1365</v>
       </c>
     </row>
     <row r="25">
@@ -1318,10 +1614,22 @@
         <v>76000</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>4.4551</v>
+        <v>3.991</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>3.6662</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0.1856</v>
       </c>
     </row>
     <row r="26">
@@ -1351,10 +1659,22 @@
         <v>73987</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>3.8789</v>
+        <v>3.2324</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>2.4423</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.5028</v>
       </c>
     </row>
     <row r="27">
@@ -1384,10 +1704,22 @@
         <v>77330</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>2.5572</v>
+        <v>2.0923</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>1.7048</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="28">
@@ -1417,10 +1749,22 @@
         <v>80000</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.456</v>
+        <v>2.2922</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>1.9238</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0.2456</v>
       </c>
     </row>
     <row r="29">
@@ -1450,10 +1794,22 @@
         <v>110316</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>3.6504</v>
+        <v>3.0199</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>2.9535</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0.0332</v>
       </c>
     </row>
     <row r="30">
@@ -1483,10 +1839,22 @@
         <v>120226</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.6073</v>
+        <v>3.7577</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>3.6924</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>0.0327</v>
       </c>
     </row>
     <row r="31">
@@ -1516,10 +1884,22 @@
         <v>126000</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>4.3411</v>
+        <v>3.7492</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>3.6505</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0.0658</v>
       </c>
     </row>
     <row r="32">
@@ -1554,6 +1934,18 @@
       <c r="I32" s="3" t="n">
         <v>6.7297</v>
       </c>
+      <c r="J32" s="3" t="n">
+        <v>5.4479</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0.9213</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1582,10 +1974,22 @@
         <v>107820</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>6.3905</v>
+        <v>6.0843</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>5.1277</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.1913</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0.1913</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0.574</v>
       </c>
     </row>
     <row r="34">
@@ -1615,10 +2019,22 @@
         <v>112000</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>7.0654</v>
+        <v>6.6015</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>6.0663</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0.2498</v>
       </c>
     </row>
     <row r="35">
@@ -1648,10 +2064,22 @@
         <v>92327</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>3.3436</v>
+        <v>3.0427</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>2.7418</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.0334</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0.2675</v>
       </c>
     </row>
     <row r="36">
@@ -1681,10 +2109,22 @@
         <v>99510</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.3406</v>
+        <v>3.408</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>2.8007</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0.4049</v>
       </c>
     </row>
     <row r="37">
@@ -1714,10 +2154,22 @@
         <v>104000</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>4.773</v>
+        <v>4.2095</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>3.7123</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0.3646</v>
       </c>
     </row>
     <row r="38">
@@ -1747,10 +2199,22 @@
         <v>39845</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.7056</v>
+        <v>4.0814</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>3.7933</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>0.096</v>
       </c>
     </row>
     <row r="39">
@@ -1780,10 +2244,22 @@
         <v>41230</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>5.0527</v>
+        <v>4.2754</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>4.1782</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1813,10 +2289,22 @@
         <v>42500</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>3.8909</v>
+        <v>3.1223</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>2.738</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.1921</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>0.1921</v>
       </c>
     </row>
     <row r="41">
@@ -1846,10 +2334,22 @@
         <v>92063</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>2.3689</v>
+        <v>2.0687</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>1.8017</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0.1001</v>
       </c>
     </row>
     <row r="42">
@@ -1879,10 +2379,22 @@
         <v>97580</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4.7345</v>
+        <v>4.1951</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>3.446</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>0.2997</v>
       </c>
     </row>
     <row r="43">
@@ -1912,10 +2424,22 @@
         <v>100000</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>4.1642</v>
+        <v>3.5116</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>3.1076</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.1243</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0.0311</v>
       </c>
     </row>
     <row r="44">
@@ -1945,10 +2469,22 @@
         <v>30185</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>2.3551</v>
+        <v>2.0991</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1.8431</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>0.0512</v>
       </c>
     </row>
     <row r="45">
@@ -1978,10 +2514,22 @@
         <v>36600</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>1.534</v>
+        <v>1.1854</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>1.0808</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2011,10 +2559,22 @@
         <v>39000</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3.2886</v>
+        <v>3.0317</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>2.7748</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2044,10 +2604,22 @@
         <v>17327</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0.8498</v>
+        <v>0.7967</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.7967</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2082,6 +2654,18 @@
       <c r="I48" s="3" t="n">
         <v>0.8343</v>
       </c>
+      <c r="J48" s="3" t="n">
+        <v>0.8343</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2115,6 +2699,18 @@
       <c r="I49" s="5" t="n">
         <v>1.3676</v>
       </c>
+      <c r="J49" s="5" t="n">
+        <v>1.3676</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2143,10 +2739,22 @@
         <v>35060</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>5.334</v>
+        <v>4.6721</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>4.0492</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0.2336</v>
       </c>
     </row>
     <row r="51">
@@ -2176,10 +2784,22 @@
         <v>36840</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>6.6991</v>
+        <v>5.9939</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>5.465</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.2204</v>
       </c>
     </row>
     <row r="52">
@@ -2209,10 +2829,22 @@
         <v>37319</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>7.1245</v>
+        <v>6.6853</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>5.7581</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>0.5368000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2242,10 +2874,22 @@
         <v>14397</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>2.091</v>
+        <v>2.0256</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>1.6989</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.196</v>
       </c>
     </row>
     <row r="54">
@@ -2275,10 +2919,22 @@
         <v>14800</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.8047</v>
+        <v>0.8852</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0.2414</v>
       </c>
     </row>
     <row r="55">
@@ -2308,10 +2964,22 @@
         <v>15000</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>2.8594</v>
+        <v>3.0344</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>2.5092</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.2918</v>
       </c>
     </row>
   </sheetData>
@@ -2325,7 +2993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2496,86 +3164,210 @@
         <v>54</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>4.1358</v>
+        <v>3.8029</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1.776</v>
+        <v>1.6833</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.8047</v>
+        <v>0.7967</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2.8623</v>
+        <v>2.7963</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4.1465</v>
+        <v>3.6894</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>5.0689</v>
+        <v>4.6661</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>8.2918</v>
+        <v>7.7124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Fintech关键词总次数</t>
+          <t>FAI-综合战略层(‱)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>54</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>106</v>
+        <v>3.3452</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>49.966</v>
+        <v>1.4139</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10</v>
+        <v>0.5633</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>69.5</v>
+        <v>2.459</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>104.5</v>
+        <v>3.4346</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>136.75</v>
+        <v>4.1759</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>229</v>
+        <v>6.3727</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>总资产(亿元)</t>
+          <t>FAI-底层算法层(‱)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>54</v>
       </c>
       <c r="C8" s="5" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.0935</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.1809</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.8882</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FAI-风控模型层(‱)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.2814</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FAI-信贷业务层(‱)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2436</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.1888</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.1959</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Fintech关键词总次数</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>97.4815</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>47.6306</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>总资产(亿元)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>148777.5556</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D12" s="5" t="n">
         <v>140680.6116</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E12" s="5" t="n">
         <v>14397</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>41547.5</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>98545</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>171507.5</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>491000</v>
       </c>
     </row>
@@ -2593,7 +3385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2603,12 +3395,15 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Table 2: Pearson相关系数矩阵</t>
+          <t>Table 2: Pearson相关系数矩阵（含四维度子FAI）</t>
         </is>
       </c>
     </row>
@@ -2640,6 +3435,26 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
+          <t>FAI-战略</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>FAI-算法</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>FAI-风控</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>FAI-信贷</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
           <t>Size(ln)</t>
         </is>
       </c>
@@ -2660,9 +3475,21 @@
         <v>-0.5849</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.5962</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="F3" s="3" t="n">
+        <v>-0.593</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-0.4281</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.2426</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.4089</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>-0.4758</v>
       </c>
     </row>
@@ -2682,9 +3509,21 @@
         <v>0.9231</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.3109</v>
+        <v>0.3001</v>
       </c>
       <c r="F4" s="5" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>0.5998</v>
       </c>
     </row>
@@ -2704,9 +3543,21 @@
         <v>1</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2218</v>
+        <v>0.1946</v>
       </c>
       <c r="F5" s="3" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.1857</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.0366</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.6204</v>
       </c>
     </row>
@@ -2717,46 +3568,206 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-0.5962</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.3109</v>
+        <v>0.3001</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.2218</v>
+        <v>0.1946</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.2939</v>
+        <v>0.9828</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.4923</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0.3264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Size(ln)</t>
+          <t>FAI-战略</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.4758</v>
+        <v>-0.593</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.5998</v>
+        <v>0.3248</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.6204</v>
+        <v>0.2482</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.2939</v>
+        <v>0.9828</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="G7" s="3" t="n">
+        <v>0.5358000000000001</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.5364</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.3294</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FAI-算法</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>-0.4281</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.5358000000000001</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.4843</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.2269</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FAI-风控</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-0.2426</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-0.1857</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.4923</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>-0.117</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FAI-信贷</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>-0.4089</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.0366</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.5364</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.4843</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.2415</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Size(ln)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-0.4758</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.6204</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-0.117</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2768,7 +3779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2836,13 +3847,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.63162</v>
+        <v>1.6274</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.05928</v>
+        <v>0.05782</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>27.526</v>
+        <v>28.146</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -2865,13 +3876,13 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-0.07736</v>
+        <v>-0.08302</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.0148</v>
+        <v>0.01486</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-5.226</v>
+        <v>-5.589</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>0</v>
@@ -2911,7 +3922,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.3555</v>
+        <v>0.3678</v>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
@@ -2930,7 +3941,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3431</v>
+        <v>0.3556</v>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
@@ -2968,13 +3979,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.00358</v>
+        <v>1.93832</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.25755</v>
+        <v>0.25515</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7.779</v>
+        <v>7.597</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -2997,13 +4008,13 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-0.05537</v>
+        <v>-0.06096</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.01201</v>
+        <v>0.01193</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-4.609</v>
+        <v>-5.111</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
@@ -3026,13 +4037,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.03618</v>
+        <v>-0.03743</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.00668</v>
+        <v>0.00701</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-5.416</v>
+        <v>-5.339</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -3055,16 +4066,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-0.01235</v>
+        <v>-0.00543</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.0245</v>
+        <v>0.02461</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.504</v>
+        <v>-0.221</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.8254</v>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
     </row>
@@ -3097,7 +4108,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.6058</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr"/>
@@ -3116,7 +4127,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5955</v>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr"/>
@@ -3154,16 +4165,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>8.35238</v>
+        <v>8.423389999999999</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2.06807</v>
+        <v>2.00109</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4.039</v>
+        <v>4.209</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -3183,16 +4194,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-0.01608</v>
+        <v>-0.01786</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.01564</v>
+        <v>0.0185</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-1.028</v>
+        <v>-0.966</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.3039</v>
+        <v>0.3343</v>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
     </row>
@@ -3208,16 +4219,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-0.02255</v>
+        <v>-0.02349</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.01356</v>
+        <v>0.01387</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-1.663</v>
+        <v>-1.693</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.0964</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -3237,16 +4248,16 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>-0.60009</v>
+        <v>-0.60524</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.17618</v>
+        <v>0.17102</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-3.406</v>
+        <v>-3.539</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -3283,7 +4294,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.945</v>
+        <v>0.9452</v>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr"/>
@@ -3302,7 +4313,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.9116</v>
+        <v>0.9119</v>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="3" t="inlineStr"/>
@@ -3328,8 +4339,380 @@
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Credit</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>截距</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1.85905</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>7.383</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Credit</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>FAI-信贷业务层</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-0.32835</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0.07212</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-4.553</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Credit</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>ROE(净资产收益率)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.04465</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Credit</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Size(ln总资产)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-0.00616</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.248</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.8042</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Credit</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>--- 模型统计 ---</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Credit</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.5554</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Credit</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Adj. R²</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0.5286999999999999</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Credit</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>观测值N</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Risk Model</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>截距</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>2.19428</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>7.465</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Risk Model</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>FAI-风控模型层</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>-0.8081</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0.27727</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>-2.914</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Risk Model</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>ROE(净资产收益率)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>-0.04098</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-4.674</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Risk Model</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Size(ln总资产)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>-0.03927</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>-1.345</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.1787</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Risk Model</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>--- 模型统计 ---</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Risk Model</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.5161</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Risk Model</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Adj. R²</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0.4871</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Sub-FAI: Risk Model</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>观测值N</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>注: *** p&lt;0.01, ** p&lt;0.05, * p&lt;0.1；括号内为异方差稳健标准误</t>
         </is>
